--- a/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260714.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260714.xlsx
@@ -1063,17 +1063,17 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>8464</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>微星</t>
+          <t>億豐</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>8,486,000</t>
+          <t>3,423,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1085,17 +1085,17 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>8464</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>億豐</t>
+          <t>微星</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>3,423,000</t>
+          <t>8,486,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -1107,17 +1107,17 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>4766</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>南寶</t>
+          <t>華碩</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>3,577,000</t>
+          <t>1,705,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -1129,17 +1129,17 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>4766</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>華碩</t>
+          <t>南寶</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>1,705,000</t>
+          <t>3,577,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1217,17 +1217,17 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>中保科</t>
+          <t>東和鋼鐵</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>10,225,000</t>
+          <t>15,639,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1239,17 +1239,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>東和鋼鐵</t>
+          <t>中保科</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>15,639,000</t>
+          <t>10,225,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
